--- a/artfynd/A 31854-2025 artfynd.xlsx
+++ b/artfynd/A 31854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126616706</v>
       </c>
       <c r="B2" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>126616600</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>126616685</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126616661</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126616636</v>
+        <v>126614343</v>
       </c>
       <c r="B6" t="n">
         <v>57817</v>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581997</v>
+        <v>582032</v>
       </c>
       <c r="R6" t="n">
-        <v>6398284</v>
+        <v>6398411</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126614343</v>
+        <v>126616636</v>
       </c>
       <c r="B7" t="n">
         <v>57817</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>582032</v>
+        <v>581997</v>
       </c>
       <c r="R7" t="n">
-        <v>6398411</v>
+        <v>6398284</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 31854-2025 artfynd.xlsx
+++ b/artfynd/A 31854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126616706</v>
       </c>
       <c r="B2" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>126616600</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>126616685</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126616661</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31854-2025 artfynd.xlsx
+++ b/artfynd/A 31854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126616706</v>
       </c>
       <c r="B2" t="n">
-        <v>105477</v>
+        <v>105471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>126616600</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>126616685</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126616661</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 31854-2025 artfynd.xlsx
+++ b/artfynd/A 31854-2025 artfynd.xlsx
@@ -675,60 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126616706</v>
+        <v>126614343</v>
       </c>
       <c r="B2" t="n">
-        <v>105477</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A  31584, Ankarsrum, Sm</t>
+          <t>A 31854, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581984</v>
+        <v>582032</v>
       </c>
       <c r="R2" t="n">
-        <v>6398284</v>
+        <v>6398411</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,46 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126616600</v>
+        <v>126616636</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,7 +837,7 @@
         <v>6398284</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126616685</v>
+        <v>126616600</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -942,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581989</v>
+        <v>581997</v>
       </c>
       <c r="R4" t="n">
-        <v>6398274</v>
+        <v>6398284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1006,7 @@
         <v>126616661</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,46 +1109,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126614343</v>
+        <v>126616685</v>
       </c>
       <c r="B6" t="n">
-        <v>57817</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,13 +1156,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>582032</v>
+        <v>581989</v>
       </c>
       <c r="R6" t="n">
-        <v>6398411</v>
+        <v>6398274</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,6 +1200,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1220,60 +1219,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126616636</v>
+        <v>126616706</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>106244</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 31854, Ankarsrum, Sm</t>
+          <t>A  31584, Ankarsrum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581997</v>
+        <v>581984</v>
       </c>
       <c r="R7" t="n">
         <v>6398284</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,6 +1310,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
